--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$141</c:f>
+              <c:f>Data!$A$2:$A$142</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$141</c:f>
+              <c:f>Data!$C$2:$C$142</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -154,12 +154,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$21</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$22</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$B$2:$B$21</c:f>
+              <c:f>WeeklyOHLC!$B$2:$B$22</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -171,12 +171,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$21</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$22</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$C$2:$C$21</c:f>
+              <c:f>WeeklyOHLC!$C$2:$C$22</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -188,12 +188,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$21</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$22</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$D$2:$D$21</c:f>
+              <c:f>WeeklyOHLC!$D$2:$D$22</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -205,12 +205,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$21</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$22</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$E$2:$E$21</c:f>
+              <c:f>WeeklyOHLC!$E$2:$E$22</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4568,8 +4568,38 @@
         </is>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-09-14 09:00:36</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>193649</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F141"/>
+  <autoFilter ref="A1:F142"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4996,8 +5026,27 @@
         <v>198797</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>193649</v>
+      </c>
+      <c r="C22">
+        <v>193649</v>
+      </c>
+      <c r="D22">
+        <v>193649</v>
+      </c>
+      <c r="E22">
+        <v>193649</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E21"/>
+  <autoFilter ref="A1:E22"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$142</c:f>
+              <c:f>Data!$A$2:$A$143</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$142</c:f>
+              <c:f>Data!$C$2:$C$143</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4598,8 +4598,38 @@
         </is>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-09-15 09:00:36</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>197552</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F142"/>
+  <autoFilter ref="A1:F143"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5036,13 +5066,13 @@
         <v>193649</v>
       </c>
       <c r="C22">
-        <v>193649</v>
+        <v>197552</v>
       </c>
       <c r="D22">
         <v>193649</v>
       </c>
       <c r="E22">
-        <v>193649</v>
+        <v>197552</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$143</c:f>
+              <c:f>Data!$A$2:$A$144</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$143</c:f>
+              <c:f>Data!$C$2:$C$144</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4628,8 +4628,38 @@
         </is>
       </c>
     </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-09-16 09:00:36</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>200658</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F143"/>
+  <autoFilter ref="A1:F144"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5066,13 +5096,13 @@
         <v>193649</v>
       </c>
       <c r="C22">
-        <v>197552</v>
+        <v>200658</v>
       </c>
       <c r="D22">
         <v>193649</v>
       </c>
       <c r="E22">
-        <v>197552</v>
+        <v>200658</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$144</c:f>
+              <c:f>Data!$A$2:$A$145</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$144</c:f>
+              <c:f>Data!$C$2:$C$145</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4658,8 +4658,38 @@
         </is>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:00:36</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>203569</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F144"/>
+  <autoFilter ref="A1:F145"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5096,13 +5126,13 @@
         <v>193649</v>
       </c>
       <c r="C22">
-        <v>200658</v>
+        <v>203569</v>
       </c>
       <c r="D22">
         <v>193649</v>
       </c>
       <c r="E22">
-        <v>200658</v>
+        <v>203569</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$145</c:f>
+              <c:f>Data!$A$2:$A$146</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$145</c:f>
+              <c:f>Data!$C$2:$C$146</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4688,8 +4688,38 @@
         </is>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:00:36</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>204255</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F145"/>
+  <autoFilter ref="A1:F146"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5126,13 +5156,13 @@
         <v>193649</v>
       </c>
       <c r="C22">
-        <v>203569</v>
+        <v>204255</v>
       </c>
       <c r="D22">
         <v>193649</v>
       </c>
       <c r="E22">
-        <v>203569</v>
+        <v>204255</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$146</c:f>
+              <c:f>Data!$A$2:$A$147</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$146</c:f>
+              <c:f>Data!$C$2:$C$147</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4718,8 +4718,38 @@
         </is>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-09-19 09:00:36</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>204004</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F146"/>
+  <autoFilter ref="A1:F147"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5162,7 +5192,7 @@
         <v>193649</v>
       </c>
       <c r="E22">
-        <v>204255</v>
+        <v>204004</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$147</c:f>
+              <c:f>Data!$A$2:$A$148</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$147</c:f>
+              <c:f>Data!$C$2:$C$148</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4748,8 +4748,38 @@
         </is>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-09-20 09:00:36</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>198990</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F147"/>
+  <autoFilter ref="A1:F148"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5192,7 +5222,7 @@
         <v>193649</v>
       </c>
       <c r="E22">
-        <v>204004</v>
+        <v>198990</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$148</c:f>
+              <c:f>Data!$A$2:$A$149</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$148</c:f>
+              <c:f>Data!$C$2:$C$149</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -154,12 +154,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$22</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$23</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$B$2:$B$22</c:f>
+              <c:f>WeeklyOHLC!$B$2:$B$23</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -171,12 +171,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$22</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$23</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$C$2:$C$22</c:f>
+              <c:f>WeeklyOHLC!$C$2:$C$23</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -188,12 +188,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$22</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$23</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$D$2:$D$22</c:f>
+              <c:f>WeeklyOHLC!$D$2:$D$23</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -205,12 +205,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$22</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$23</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$E$2:$E$22</c:f>
+              <c:f>WeeklyOHLC!$E$2:$E$23</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4778,8 +4778,38 @@
         </is>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-09-21 09:00:36</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>193069</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F148"/>
+  <autoFilter ref="A1:F149"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5225,8 +5255,27 @@
         <v>198990</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>193069</v>
+      </c>
+      <c r="C23">
+        <v>193069</v>
+      </c>
+      <c r="D23">
+        <v>193069</v>
+      </c>
+      <c r="E23">
+        <v>193069</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E22"/>
+  <autoFilter ref="A1:E23"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$149</c:f>
+              <c:f>Data!$A$2:$A$150</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$149</c:f>
+              <c:f>Data!$C$2:$C$150</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4808,8 +4808,38 @@
         </is>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-09-22 09:00:36</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>196196</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F149"/>
+  <autoFilter ref="A1:F150"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5265,13 +5295,13 @@
         <v>193069</v>
       </c>
       <c r="C23">
-        <v>193069</v>
+        <v>196196</v>
       </c>
       <c r="D23">
         <v>193069</v>
       </c>
       <c r="E23">
-        <v>193069</v>
+        <v>196196</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$150</c:f>
+              <c:f>Data!$A$2:$A$151</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$150</c:f>
+              <c:f>Data!$C$2:$C$151</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4838,8 +4838,38 @@
         </is>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-09-23 09:00:36</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>198640</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F150"/>
+  <autoFilter ref="A1:F151"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5295,13 +5325,13 @@
         <v>193069</v>
       </c>
       <c r="C23">
-        <v>196196</v>
+        <v>198640</v>
       </c>
       <c r="D23">
         <v>193069</v>
       </c>
       <c r="E23">
-        <v>196196</v>
+        <v>198640</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$151</c:f>
+              <c:f>Data!$A$2:$A$152</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$151</c:f>
+              <c:f>Data!$C$2:$C$152</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4868,8 +4868,38 @@
         </is>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:00:36</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>198418</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F151"/>
+  <autoFilter ref="A1:F152"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5331,7 +5361,7 @@
         <v>193069</v>
       </c>
       <c r="E23">
-        <v>198640</v>
+        <v>198418</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$152</c:f>
+              <c:f>Data!$A$2:$A$153</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$152</c:f>
+              <c:f>Data!$C$2:$C$153</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4898,8 +4898,38 @@
         </is>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:00:36</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>195762</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F152"/>
+  <autoFilter ref="A1:F153"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5361,7 +5391,7 @@
         <v>193069</v>
       </c>
       <c r="E23">
-        <v>198418</v>
+        <v>195762</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$153</c:f>
+              <c:f>Data!$A$2:$A$154</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$153</c:f>
+              <c:f>Data!$C$2:$C$154</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4928,8 +4928,38 @@
         </is>
       </c>
     </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-09-26 09:00:36</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>191849</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F153"/>
+  <autoFilter ref="A1:F154"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5388,10 +5418,10 @@
         <v>198640</v>
       </c>
       <c r="D23">
-        <v>193069</v>
+        <v>191849</v>
       </c>
       <c r="E23">
-        <v>195762</v>
+        <v>191849</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$154</c:f>
+              <c:f>Data!$A$2:$A$155</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$154</c:f>
+              <c:f>Data!$C$2:$C$155</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4958,8 +4958,38 @@
         </is>
       </c>
     </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-09-27 09:00:36</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>187126</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F154"/>
+  <autoFilter ref="A1:F155"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5418,10 +5448,10 @@
         <v>198640</v>
       </c>
       <c r="D23">
-        <v>191849</v>
+        <v>187126</v>
       </c>
       <c r="E23">
-        <v>191849</v>
+        <v>187126</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$155</c:f>
+              <c:f>Data!$A$2:$A$156</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$155</c:f>
+              <c:f>Data!$C$2:$C$156</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -154,12 +154,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$23</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$24</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$B$2:$B$23</c:f>
+              <c:f>WeeklyOHLC!$B$2:$B$24</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -171,12 +171,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$23</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$24</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$C$2:$C$23</c:f>
+              <c:f>WeeklyOHLC!$C$2:$C$24</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -188,12 +188,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$23</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$24</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$D$2:$D$23</c:f>
+              <c:f>WeeklyOHLC!$D$2:$D$24</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -205,12 +205,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$23</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$24</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$E$2:$E$23</c:f>
+              <c:f>WeeklyOHLC!$E$2:$E$24</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -4988,8 +4988,38 @@
         </is>
       </c>
     </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:00:36</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>182099</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F155"/>
+  <autoFilter ref="A1:F156"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5454,8 +5484,27 @@
         <v>187126</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>182099</v>
+      </c>
+      <c r="C24">
+        <v>182099</v>
+      </c>
+      <c r="D24">
+        <v>182099</v>
+      </c>
+      <c r="E24">
+        <v>182099</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E23"/>
+  <autoFilter ref="A1:E24"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$156</c:f>
+              <c:f>Data!$A$2:$A$157</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$156</c:f>
+              <c:f>Data!$C$2:$C$157</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5018,8 +5018,38 @@
         </is>
       </c>
     </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:00:36</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>188407</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F156"/>
+  <autoFilter ref="A1:F157"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5494,13 +5524,13 @@
         <v>182099</v>
       </c>
       <c r="C24">
-        <v>182099</v>
+        <v>188407</v>
       </c>
       <c r="D24">
         <v>182099</v>
       </c>
       <c r="E24">
-        <v>182099</v>
+        <v>188407</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$157</c:f>
+              <c:f>Data!$A$2:$A$158</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$157</c:f>
+              <c:f>Data!$C$2:$C$158</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5048,8 +5048,38 @@
         </is>
       </c>
     </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:00:36</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>192484</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F157"/>
+  <autoFilter ref="A1:F158"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5524,13 +5554,13 @@
         <v>182099</v>
       </c>
       <c r="C24">
-        <v>188407</v>
+        <v>192484</v>
       </c>
       <c r="D24">
         <v>182099</v>
       </c>
       <c r="E24">
-        <v>188407</v>
+        <v>192484</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$158</c:f>
+              <c:f>Data!$A$2:$A$159</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$158</c:f>
+              <c:f>Data!$C$2:$C$159</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5078,8 +5078,38 @@
         </is>
       </c>
     </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-10-01 09:00:36</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>185956</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F158"/>
+  <autoFilter ref="A1:F159"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5560,7 +5590,7 @@
         <v>182099</v>
       </c>
       <c r="E24">
-        <v>192484</v>
+        <v>185956</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$159</c:f>
+              <c:f>Data!$A$2:$A$160</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$159</c:f>
+              <c:f>Data!$C$2:$C$160</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5108,8 +5108,38 @@
         </is>
       </c>
     </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-10-02 09:00:36</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>190534</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F159"/>
+  <autoFilter ref="A1:F160"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5590,7 +5620,7 @@
         <v>182099</v>
       </c>
       <c r="E24">
-        <v>185956</v>
+        <v>190534</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$160</c:f>
+              <c:f>Data!$A$2:$A$161</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$160</c:f>
+              <c:f>Data!$C$2:$C$161</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5138,8 +5138,38 @@
         </is>
       </c>
     </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-10-03 09:00:36</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>192012</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F160"/>
+  <autoFilter ref="A1:F161"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5620,7 +5650,7 @@
         <v>182099</v>
       </c>
       <c r="E24">
-        <v>190534</v>
+        <v>192012</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$161</c:f>
+              <c:f>Data!$A$2:$A$162</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$161</c:f>
+              <c:f>Data!$C$2:$C$162</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5168,8 +5168,38 @@
         </is>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-10-04 09:00:36</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>187719</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F161"/>
+  <autoFilter ref="A1:F162"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5650,7 +5680,7 @@
         <v>182099</v>
       </c>
       <c r="E24">
-        <v>192012</v>
+        <v>187719</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$162</c:f>
+              <c:f>Data!$A$2:$A$163</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$162</c:f>
+              <c:f>Data!$C$2:$C$163</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -154,12 +154,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$24</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$25</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$B$2:$B$24</c:f>
+              <c:f>WeeklyOHLC!$B$2:$B$25</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -171,12 +171,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$24</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$25</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$C$2:$C$24</c:f>
+              <c:f>WeeklyOHLC!$C$2:$C$25</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -188,12 +188,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$24</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$25</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$D$2:$D$24</c:f>
+              <c:f>WeeklyOHLC!$D$2:$D$25</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -205,12 +205,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$24</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$25</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$E$2:$E$24</c:f>
+              <c:f>WeeklyOHLC!$E$2:$E$25</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5198,8 +5198,38 @@
         </is>
       </c>
     </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:00:36</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>183691</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F162"/>
+  <autoFilter ref="A1:F163"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5683,8 +5713,27 @@
         <v>187719</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>183691</v>
+      </c>
+      <c r="C25">
+        <v>183691</v>
+      </c>
+      <c r="D25">
+        <v>183691</v>
+      </c>
+      <c r="E25">
+        <v>183691</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E24"/>
+  <autoFilter ref="A1:E25"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$163</c:f>
+              <c:f>Data!$A$2:$A$164</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$163</c:f>
+              <c:f>Data!$C$2:$C$164</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5228,8 +5228,38 @@
         </is>
       </c>
     </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:00:36</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>180523</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F163"/>
+  <autoFilter ref="A1:F164"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5726,10 +5756,10 @@
         <v>183691</v>
       </c>
       <c r="D25">
-        <v>183691</v>
+        <v>180523</v>
       </c>
       <c r="E25">
-        <v>183691</v>
+        <v>180523</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$164</c:f>
+              <c:f>Data!$A$2:$A$165</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$164</c:f>
+              <c:f>Data!$C$2:$C$165</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5258,8 +5258,38 @@
         </is>
       </c>
     </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:00:36</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>187095</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F164"/>
+  <autoFilter ref="A1:F165"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5753,13 +5783,13 @@
         <v>183691</v>
       </c>
       <c r="C25">
-        <v>183691</v>
+        <v>187095</v>
       </c>
       <c r="D25">
         <v>180523</v>
       </c>
       <c r="E25">
-        <v>180523</v>
+        <v>187095</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$165</c:f>
+              <c:f>Data!$A$2:$A$166</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$165</c:f>
+              <c:f>Data!$C$2:$C$166</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5288,8 +5288,38 @@
         </is>
       </c>
     </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-10-08 09:00:36</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>190776</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F165"/>
+  <autoFilter ref="A1:F166"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5783,13 +5813,13 @@
         <v>183691</v>
       </c>
       <c r="C25">
-        <v>187095</v>
+        <v>190776</v>
       </c>
       <c r="D25">
         <v>180523</v>
       </c>
       <c r="E25">
-        <v>187095</v>
+        <v>190776</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$166</c:f>
+              <c:f>Data!$A$2:$A$167</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$166</c:f>
+              <c:f>Data!$C$2:$C$167</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5318,8 +5318,38 @@
         </is>
       </c>
     </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:00:36</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>194217</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F166"/>
+  <autoFilter ref="A1:F167"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5813,13 +5843,13 @@
         <v>183691</v>
       </c>
       <c r="C25">
-        <v>190776</v>
+        <v>194217</v>
       </c>
       <c r="D25">
         <v>180523</v>
       </c>
       <c r="E25">
-        <v>190776</v>
+        <v>194217</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$167</c:f>
+              <c:f>Data!$A$2:$A$168</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$167</c:f>
+              <c:f>Data!$C$2:$C$168</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5348,8 +5348,38 @@
         </is>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-10-10 09:00:36</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>189444</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F167"/>
+  <autoFilter ref="A1:F168"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5849,7 +5879,7 @@
         <v>180523</v>
       </c>
       <c r="E25">
-        <v>194217</v>
+        <v>189444</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$168</c:f>
+              <c:f>Data!$A$2:$A$169</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$168</c:f>
+              <c:f>Data!$C$2:$C$169</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5378,8 +5378,38 @@
         </is>
       </c>
     </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-10-11 09:00:36</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>184781</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F168"/>
+  <autoFilter ref="A1:F169"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5879,7 +5909,7 @@
         <v>180523</v>
       </c>
       <c r="E25">
-        <v>189444</v>
+        <v>184781</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$169</c:f>
+              <c:f>Data!$A$2:$A$170</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$169</c:f>
+              <c:f>Data!$C$2:$C$170</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -154,12 +154,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$25</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$26</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$B$2:$B$25</c:f>
+              <c:f>WeeklyOHLC!$B$2:$B$26</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -171,12 +171,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$25</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$26</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$C$2:$C$25</c:f>
+              <c:f>WeeklyOHLC!$C$2:$C$26</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -188,12 +188,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$25</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$26</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$D$2:$D$25</c:f>
+              <c:f>WeeklyOHLC!$D$2:$D$26</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -205,12 +205,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$25</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$26</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$E$2:$E$25</c:f>
+              <c:f>WeeklyOHLC!$E$2:$E$26</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5408,8 +5408,38 @@
         </is>
       </c>
     </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-10-12 09:00:36</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>179870</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F169"/>
+  <autoFilter ref="A1:F170"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5912,8 +5942,27 @@
         <v>184781</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>179870</v>
+      </c>
+      <c r="C26">
+        <v>179870</v>
+      </c>
+      <c r="D26">
+        <v>179870</v>
+      </c>
+      <c r="E26">
+        <v>179870</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E25"/>
+  <autoFilter ref="A1:E26"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$170</c:f>
+              <c:f>Data!$A$2:$A$171</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$170</c:f>
+              <c:f>Data!$C$2:$C$171</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5438,8 +5438,38 @@
         </is>
       </c>
     </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:00:36</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>184939</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F170"/>
+  <autoFilter ref="A1:F171"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5952,13 +5982,13 @@
         <v>179870</v>
       </c>
       <c r="C26">
-        <v>179870</v>
+        <v>184939</v>
       </c>
       <c r="D26">
         <v>179870</v>
       </c>
       <c r="E26">
-        <v>179870</v>
+        <v>184939</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$171</c:f>
+              <c:f>Data!$A$2:$A$172</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$171</c:f>
+              <c:f>Data!$C$2:$C$172</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5468,8 +5468,38 @@
         </is>
       </c>
     </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:00:36</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>189537</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F171"/>
+  <autoFilter ref="A1:F172"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5982,13 +6012,13 @@
         <v>179870</v>
       </c>
       <c r="C26">
-        <v>184939</v>
+        <v>189537</v>
       </c>
       <c r="D26">
         <v>179870</v>
       </c>
       <c r="E26">
-        <v>184939</v>
+        <v>189537</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$172</c:f>
+              <c:f>Data!$A$2:$A$173</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$172</c:f>
+              <c:f>Data!$C$2:$C$173</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5498,8 +5498,38 @@
         </is>
       </c>
     </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:00:36</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>192108</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F172"/>
+  <autoFilter ref="A1:F173"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6012,13 +6042,13 @@
         <v>179870</v>
       </c>
       <c r="C26">
-        <v>189537</v>
+        <v>192108</v>
       </c>
       <c r="D26">
         <v>179870</v>
       </c>
       <c r="E26">
-        <v>189537</v>
+        <v>192108</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$173</c:f>
+              <c:f>Data!$A$2:$A$174</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$173</c:f>
+              <c:f>Data!$C$2:$C$174</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5528,8 +5528,38 @@
         </is>
       </c>
     </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:00:36</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>194098</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F173"/>
+  <autoFilter ref="A1:F174"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6042,13 +6072,13 @@
         <v>179870</v>
       </c>
       <c r="C26">
-        <v>192108</v>
+        <v>194098</v>
       </c>
       <c r="D26">
         <v>179870</v>
       </c>
       <c r="E26">
-        <v>192108</v>
+        <v>194098</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$174</c:f>
+              <c:f>Data!$A$2:$A$175</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$174</c:f>
+              <c:f>Data!$C$2:$C$175</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5558,8 +5558,38 @@
         </is>
       </c>
     </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-10-17 09:00:36</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>195744</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F174"/>
+  <autoFilter ref="A1:F175"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6072,13 +6102,13 @@
         <v>179870</v>
       </c>
       <c r="C26">
-        <v>194098</v>
+        <v>195744</v>
       </c>
       <c r="D26">
         <v>179870</v>
       </c>
       <c r="E26">
-        <v>194098</v>
+        <v>195744</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$175</c:f>
+              <c:f>Data!$A$2:$A$176</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$175</c:f>
+              <c:f>Data!$C$2:$C$176</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5588,8 +5588,38 @@
         </is>
       </c>
     </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-10-18 09:00:36</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>190853</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F175"/>
+  <autoFilter ref="A1:F176"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6108,7 +6138,7 @@
         <v>179870</v>
       </c>
       <c r="E26">
-        <v>195744</v>
+        <v>190853</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$176</c:f>
+              <c:f>Data!$A$2:$A$177</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$176</c:f>
+              <c:f>Data!$C$2:$C$177</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -154,12 +154,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$26</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$27</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$B$2:$B$26</c:f>
+              <c:f>WeeklyOHLC!$B$2:$B$27</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -171,12 +171,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$26</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$27</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$C$2:$C$26</c:f>
+              <c:f>WeeklyOHLC!$C$2:$C$27</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -188,12 +188,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$26</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$27</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$D$2:$D$26</c:f>
+              <c:f>WeeklyOHLC!$D$2:$D$27</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -205,12 +205,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$26</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$27</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$E$2:$E$26</c:f>
+              <c:f>WeeklyOHLC!$E$2:$E$27</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5618,8 +5618,38 @@
         </is>
       </c>
     </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-10-19 09:00:36</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>185580</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F176"/>
+  <autoFilter ref="A1:F177"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6141,8 +6171,27 @@
         <v>190853</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>185580</v>
+      </c>
+      <c r="C27">
+        <v>185580</v>
+      </c>
+      <c r="D27">
+        <v>185580</v>
+      </c>
+      <c r="E27">
+        <v>185580</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E26"/>
+  <autoFilter ref="A1:E27"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$177</c:f>
+              <c:f>Data!$A$2:$A$178</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$177</c:f>
+              <c:f>Data!$C$2:$C$178</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5648,8 +5648,38 @@
         </is>
       </c>
     </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-10-20 09:00:36</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>190636</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F177"/>
+  <autoFilter ref="A1:F178"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6181,13 +6211,13 @@
         <v>185580</v>
       </c>
       <c r="C27">
-        <v>185580</v>
+        <v>190636</v>
       </c>
       <c r="D27">
         <v>185580</v>
       </c>
       <c r="E27">
-        <v>185580</v>
+        <v>190636</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$178</c:f>
+              <c:f>Data!$A$2:$A$179</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$178</c:f>
+              <c:f>Data!$C$2:$C$179</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5678,8 +5678,38 @@
         </is>
       </c>
     </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-10-21 09:00:36</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>192944</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F178"/>
+  <autoFilter ref="A1:F179"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6211,13 +6241,13 @@
         <v>185580</v>
       </c>
       <c r="C27">
-        <v>190636</v>
+        <v>192944</v>
       </c>
       <c r="D27">
         <v>185580</v>
       </c>
       <c r="E27">
-        <v>190636</v>
+        <v>192944</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$179</c:f>
+              <c:f>Data!$A$2:$A$180</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$179</c:f>
+              <c:f>Data!$C$2:$C$180</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5708,8 +5708,38 @@
         </is>
       </c>
     </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:00:36</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>194656</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F179"/>
+  <autoFilter ref="A1:F180"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6241,13 +6271,13 @@
         <v>185580</v>
       </c>
       <c r="C27">
-        <v>192944</v>
+        <v>194656</v>
       </c>
       <c r="D27">
         <v>185580</v>
       </c>
       <c r="E27">
-        <v>192944</v>
+        <v>194656</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$180</c:f>
+              <c:f>Data!$A$2:$A$181</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$180</c:f>
+              <c:f>Data!$C$2:$C$181</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5738,8 +5738,38 @@
         </is>
       </c>
     </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-10-23 09:00:36</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>197021</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F180"/>
+  <autoFilter ref="A1:F181"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6271,13 +6301,13 @@
         <v>185580</v>
       </c>
       <c r="C27">
-        <v>194656</v>
+        <v>197021</v>
       </c>
       <c r="D27">
         <v>185580</v>
       </c>
       <c r="E27">
-        <v>194656</v>
+        <v>197021</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$181</c:f>
+              <c:f>Data!$A$2:$A$182</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$181</c:f>
+              <c:f>Data!$C$2:$C$182</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5768,8 +5768,38 @@
         </is>
       </c>
     </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-10-24 09:00:36</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>196395</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F181"/>
+  <autoFilter ref="A1:F182"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6307,7 +6337,7 @@
         <v>185580</v>
       </c>
       <c r="E27">
-        <v>197021</v>
+        <v>196395</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$182</c:f>
+              <c:f>Data!$A$2:$A$183</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$182</c:f>
+              <c:f>Data!$C$2:$C$183</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5798,8 +5798,38 @@
         </is>
       </c>
     </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-10-25 09:01:39</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>193371</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F182"/>
+  <autoFilter ref="A1:F183"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6337,7 +6367,7 @@
         <v>185580</v>
       </c>
       <c r="E27">
-        <v>196395</v>
+        <v>193371</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$183</c:f>
+              <c:f>Data!$A$2:$A$184</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$183</c:f>
+              <c:f>Data!$C$2:$C$184</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -154,12 +154,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$27</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$28</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$B$2:$B$27</c:f>
+              <c:f>WeeklyOHLC!$B$2:$B$28</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -171,12 +171,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$27</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$28</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$C$2:$C$27</c:f>
+              <c:f>WeeklyOHLC!$C$2:$C$28</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -188,12 +188,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$27</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$28</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$D$2:$D$27</c:f>
+              <c:f>WeeklyOHLC!$D$2:$D$28</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -205,12 +205,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>WeeklyOHLC!$A$2:$A$27</c:f>
+              <c:f>WeeklyOHLC!$A$2:$A$28</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>WeeklyOHLC!$E$2:$E$27</c:f>
+              <c:f>WeeklyOHLC!$E$2:$E$28</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5828,8 +5828,38 @@
         </is>
       </c>
     </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:00:36</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>189311</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F183"/>
+  <autoFilter ref="A1:F184"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6370,8 +6400,27 @@
         <v>193371</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>189311</v>
+      </c>
+      <c r="C28">
+        <v>189311</v>
+      </c>
+      <c r="D28">
+        <v>189311</v>
+      </c>
+      <c r="E28">
+        <v>189311</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E27"/>
+  <autoFilter ref="A1:E28"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$184</c:f>
+              <c:f>Data!$A$2:$A$185</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$184</c:f>
+              <c:f>Data!$C$2:$C$185</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5858,8 +5858,38 @@
         </is>
       </c>
     </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:00:36</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>192721</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F184"/>
+  <autoFilter ref="A1:F185"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6410,13 +6440,13 @@
         <v>189311</v>
       </c>
       <c r="C28">
-        <v>189311</v>
+        <v>192721</v>
       </c>
       <c r="D28">
         <v>189311</v>
       </c>
       <c r="E28">
-        <v>189311</v>
+        <v>192721</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$185</c:f>
+              <c:f>Data!$A$2:$A$186</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$185</c:f>
+              <c:f>Data!$C$2:$C$186</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5888,8 +5888,38 @@
         </is>
       </c>
     </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:00:36</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>195552</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F185"/>
+  <autoFilter ref="A1:F186"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6440,13 +6470,13 @@
         <v>189311</v>
       </c>
       <c r="C28">
-        <v>192721</v>
+        <v>195552</v>
       </c>
       <c r="D28">
         <v>189311</v>
       </c>
       <c r="E28">
-        <v>192721</v>
+        <v>195552</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$186</c:f>
+              <c:f>Data!$A$2:$A$187</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$186</c:f>
+              <c:f>Data!$C$2:$C$187</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5918,8 +5918,38 @@
         </is>
       </c>
     </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-10-29 09:00:36</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>196683</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F186"/>
+  <autoFilter ref="A1:F187"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6470,13 +6500,13 @@
         <v>189311</v>
       </c>
       <c r="C28">
-        <v>195552</v>
+        <v>196683</v>
       </c>
       <c r="D28">
         <v>189311</v>
       </c>
       <c r="E28">
-        <v>195552</v>
+        <v>196683</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$187</c:f>
+              <c:f>Data!$A$2:$A$188</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$187</c:f>
+              <c:f>Data!$C$2:$C$188</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5948,8 +5948,38 @@
         </is>
       </c>
     </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-10-30 09:00:36</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>197959</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F187"/>
+  <autoFilter ref="A1:F188"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6500,13 +6530,13 @@
         <v>189311</v>
       </c>
       <c r="C28">
-        <v>196683</v>
+        <v>197959</v>
       </c>
       <c r="D28">
         <v>189311</v>
       </c>
       <c r="E28">
-        <v>196683</v>
+        <v>197959</v>
       </c>
     </row>
   </sheetData>

--- a/data/job_post_counts.xlsx
+++ b/data/job_post_counts.xlsx
@@ -81,12 +81,12 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>Data!$A$2:$A$188</c:f>
+              <c:f>Data!$A$2:$A$189</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Data!$C$2:$C$188</c:f>
+              <c:f>Data!$C$2:$C$189</c:f>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -5978,8 +5978,38 @@
         </is>
       </c>
     </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-10-31 09:00:36</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>195034</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>parsed joblist hdnGICnt</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>https://www.jobkorea.co.kr/recruit/joblist?menucode=local&amp;localorder=1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F188"/>
+  <autoFilter ref="A1:F189"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6536,7 +6566,7 @@
         <v>189311</v>
       </c>
       <c r="E28">
-        <v>197959</v>
+        <v>195034</v>
       </c>
     </row>
   </sheetData>
